--- a/Result/profitability/8941.xlsx
+++ b/Result/profitability/8941.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.61625</v>
       </c>
       <c r="N2" t="n">
-        <v>27.41125</v>
+        <v>26.95875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4537499999999999</v>
+        <v>0.4862499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>26.02875</v>
+        <v>25.5925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29125</v>
+        <v>0.2175</v>
       </c>
       <c r="N4" t="n">
-        <v>24.02625</v>
+        <v>23.6775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1725000000000001</v>
+        <v>0.09749999999999992</v>
       </c>
       <c r="N5" t="n">
-        <v>23.14875</v>
+        <v>22.65875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.82</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1300000000000001</v>
+        <v>-0.01125000000000008</v>
       </c>
       <c r="N6" t="n">
-        <v>22.9825</v>
+        <v>22.66125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.95</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2550000000000001</v>
+        <v>-0.2150000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>24.72875</v>
+        <v>23.8425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5250000000000001</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>22.92375</v>
+        <v>22.37125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8941</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>818</v>
+      </c>
+      <c r="D75" t="n">
+        <v>613</v>
+      </c>
+      <c r="E75" t="n">
+        <v>205</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.48%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>52</v>
+      </c>
+      <c r="J75" t="n">
+        <v>40</v>
+      </c>
+      <c r="K75" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7112499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.4975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.3600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2647058823529412</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.419999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1501868841318382</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.862068965517242</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.919999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.135499481507086</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
